--- a/public/plantilla-estudiantes.xlsx
+++ b/public/plantilla-estudiantes.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -458,292 +458,297 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">   - Ejemplo: ANA PAOLA RÍOS MARTÍNEZ</v>
+        <v xml:space="preserve">   - IMPORTANTE: En Firmantes, NO marcar "Firmante fijo"</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v xml:space="preserve">   - Ejemplo: ANA PAOLA RÍOS MARTÍNEZ</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2. municipio</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">   - Municipio donde está ubicada la institución educativa</v>
+        <v>2. municipio</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">   - Ejemplo: Montería, Planeta Rica, Cereté</v>
+        <v xml:space="preserve">   - Municipio donde está ubicada la institución educativa</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v xml:space="preserve">   - Ejemplo: Montería, Planeta Rica, Cereté</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3. institucion educativa</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">   - Nombre completo de la institución educativa</v>
+        <v>3. institucion educativa</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">   - Si la institución ya existe, se actualizará la fecha y contratista</v>
+        <v xml:space="preserve">   - Nombre completo de la institución educativa</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">   - Si no existe, se creará automáticamente</v>
+        <v xml:space="preserve">   - Si la institución ya existe, se actualizará la fecha y contratista</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">   - Ejemplo: Institución Educativa Simón Bolívar</v>
+        <v xml:space="preserve">   - Si no existe, se creará automáticamente</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v xml:space="preserve">   - Ejemplo: Institución Educativa Simón Bolívar</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>4. NOMBRE COMPLETO DEL ALUMNO</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">   - Nombre completo del estudiante</v>
+        <v>4. NOMBRE COMPLETO DEL ALUMNO</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">   - Usa mayúsculas, minúsculas o mezcla, el sistema lo normaliza</v>
+        <v xml:space="preserve">   - Nombre completo del estudiante</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">   - Incluir apellidos completos</v>
+        <v xml:space="preserve">   - Usa mayúsculas, minúsculas o mezcla, el sistema lo normaliza</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">   - Ejemplo: JUAN CAMILO PÉREZ GÓMEZ</v>
+        <v xml:space="preserve">   - Incluir apellidos completos</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v xml:space="preserve">   - Ejemplo: JUAN CAMILO PÉREZ GÓMEZ</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>5. TIPO DE DOCUMENTO</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">   - Tipo de documento de identidad</v>
+        <v>5. TIPO DE DOCUMENTO</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">   - Valores válidos:</v>
+        <v xml:space="preserve">   - Tipo de documento de identidad</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">     • RC  - Registro Civil</v>
+        <v xml:space="preserve">   - Valores válidos:</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v xml:space="preserve">     • TI  - Tarjeta de Identidad</v>
+        <v xml:space="preserve">     • RC  - Registro Civil</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">     • CC  - Cédula de Ciudadanía</v>
+        <v xml:space="preserve">     • TI  - Tarjeta de Identidad</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">     • CE  - Cédula de Extranjería</v>
+        <v xml:space="preserve">     • CC  - Cédula de Ciudadanía</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">     • PPT - Permiso por Protección Temporal</v>
+        <v xml:space="preserve">     • CE  - Cédula de Extranjería</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">     • PEP - Permiso Especial de Permanencia</v>
+        <v xml:space="preserve">     • PPT - Permiso por Protección Temporal</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">   - Acepta formatos como: TI, T.I., TARJETA DE IDENTIDAD, etc.</v>
+        <v xml:space="preserve">     • PEP - Permiso Especial de Permanencia</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v xml:space="preserve">   - Acepta formatos como: TI, T.I., TARJETA DE IDENTIDAD, etc.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>6. NUMERO DE DOCUMENTO</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">   - Número de documento sin puntos, ni espacios, ni comas</v>
+        <v>6. NUMERO DE DOCUMENTO</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">   - El sistema lo normaliza automáticamente</v>
+        <v xml:space="preserve">   - Número de documento sin puntos, ni espacios, ni comas</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">   - Ejemplos válidos: 1234567890, 12345678</v>
+        <v xml:space="preserve">   - El sistema lo normaliza automáticamente</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v xml:space="preserve">   - Ejemplos que se normalizan: 1.234.567.890 → 1234567890</v>
+        <v xml:space="preserve">   - Ejemplos válidos: 1234567890, 12345678</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v xml:space="preserve">   - Ejemplos que se normalizan: 1.234.567.890 → 1234567890</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>7. fecha de entrega del certificado</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">   - Fecha en que se entregará el certificado</v>
+        <v>7. fecha de entrega del certificado</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v xml:space="preserve">   - Formatos aceptados: DD/MM/AAAA o AAAA-MM-DD</v>
+        <v xml:space="preserve">   - Fecha en que se entregará el certificado</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">   - Ejemplos: 15/11/2026 o 2026-11-15</v>
+        <v xml:space="preserve">   - Formatos aceptados: DD/MM/AAAA o AAAA-MM-DD</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v/>
+        <v xml:space="preserve">   - Ejemplos: 15/11/2026 o 2026-11-15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Reglas importantes:</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Reglas importantes:</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>• No dejes filas vacías entre los datos</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>• No cambies el nombre de las columnas</v>
+        <v>• No dejes filas vacías entre los datos</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>• Verifica que el contratista esté registrado en Firmantes antes de importar</v>
+        <v>• No cambies el nombre de las columnas</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>• Cada combinación institución+municipio+contratista+fecha crea una jornada</v>
+        <v>• Verifica que el contratista esté registrado en Firmantes antes de importar</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>• Los documentos duplicados en el mismo archivo generarán error</v>
+        <v>• Cada combinación institución+municipio+contratista+fecha crea una jornada</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>• Se pueden importar múltiples instituciones en un solo archivo</v>
+        <v>• Los documentos duplicados en el mismo archivo generarán error</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>• Se pueden importar múltiples instituciones en un solo archivo</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Antes de importar:</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v/>
+        <v>Antes de importar:</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>1. Registra los contratistas en el panel admin (Firmantes)</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2. Sube las firmas de los contratistas al sistema</v>
+        <v>1. Registra los contratistas en el panel admin (Firmantes)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>3. Asigna los firmantes a las instituciones correspondientes</v>
+        <v>2. Sube las firmas de los contratistas al sistema</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>4. Luego importa este archivo en Estudiantes → Importar Excel</v>
+        <v>3. Asigna los firmantes a las instituciones correspondientes</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>4. Luego importa este archivo en Estudiantes → Importar Excel</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
         <v>Para ayuda, contacta al administrador del sistema.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A69"/>
   </ignoredErrors>
 </worksheet>
 </file>
